--- a/data/file_generation/input/data_57/2025-10-12_10_35_美职业_洛杉矶银河[西15]VS达拉斯FC[西8]_标盘.xlsx
+++ b/data/file_generation/input/data_57/2025-10-12_10_35_美职业_洛杉矶银河[西15]VS达拉斯FC[西8]_标盘.xlsx
@@ -26358,26 +26358,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A56C6D2D-F1B5-4C56-ACF4-22A893FB8439}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{657A4B2A-6527-428D-B6DD-07B7C3CEBB51}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{372D311E-3CCC-4B59-8EC0-D24969D3DD5F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29D17C60-A7FA-4C75-8E84-E004A425414E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C71099A1-7CE6-4F9A-AAF9-21483FB22A59}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36E1C7F9-DEA4-48E1-9FED-70C56DF4AE21}"/>
 </file>